--- a/artfynd/A 36966-2022 artfynd.xlsx
+++ b/artfynd/A 36966-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,59 +792,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131666524</v>
+        <v>137312248</v>
       </c>
       <c r="B3" t="n">
-        <v>99195</v>
+        <v>93455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Slånget, Slånget, Dlr</t>
+          <t>Falun/Borlänge/Insjön, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525789</v>
+        <v>525881</v>
       </c>
       <c r="R3" t="n">
-        <v>6717906</v>
+        <v>6717939</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,22 +866,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,16 +896,142 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137312248</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131666524</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Slånget, Slånget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>525789</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6717906</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131666524</t>
         </is>
@@ -920,6 +1041,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36966-2022 artfynd.xlsx
+++ b/artfynd/A 36966-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137312248</v>
       </c>
       <c r="B3" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36966-2022 artfynd.xlsx
+++ b/artfynd/A 36966-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137312248</v>
       </c>
       <c r="B3" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36966-2022 artfynd.xlsx
+++ b/artfynd/A 36966-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137312248</v>
       </c>
       <c r="B3" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36966-2022 artfynd.xlsx
+++ b/artfynd/A 36966-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137312248</v>
       </c>
       <c r="B3" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36966-2022 artfynd.xlsx
+++ b/artfynd/A 36966-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137312248</v>
       </c>
       <c r="B3" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36966-2022 artfynd.xlsx
+++ b/artfynd/A 36966-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137312248</v>
       </c>
       <c r="B3" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36966-2022 artfynd.xlsx
+++ b/artfynd/A 36966-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137312248</v>
       </c>
       <c r="B3" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36966-2022 artfynd.xlsx
+++ b/artfynd/A 36966-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137312248</v>
       </c>
       <c r="B3" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
